--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484098_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484098_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7345</v>
+        <v>2.3344</v>
       </c>
       <c r="E2" t="n">
-        <v>1.994</v>
+        <v>0.2864</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7405</v>
+        <v>2.048</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0638</v>
+        <v>0.1074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1713</v>
+        <v>-0.232</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1075</v>
+        <v>0.3394</v>
       </c>
       <c r="J2" t="n">
-        <v>2.364</v>
+        <v>0.0256</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3533</v>
+        <v>-0.5794</v>
       </c>
       <c r="L2" t="n">
-        <v>2.0106</v>
+        <v>0.605</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.3002</v>
+        <v>0.0818</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1821</v>
+        <v>0.3474</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1181</v>
+        <v>-0.2656</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.9758</v>
+        <v>0.7935</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.1661</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7576</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0577</v>
+        <v>0.2608</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6999</v>
+        <v>0.3556</v>
       </c>
       <c r="V2" t="n">
-        <v>2.8889</v>
+        <v>0.8171</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1505</v>
+        <v>0.8171</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2389</v>
+        <v>1.316</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2861</v>
+        <v>0.9964</v>
       </c>
       <c r="F3" t="n">
-        <v>2.525</v>
+        <v>0.3196</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1074</v>
+        <v>0.0638</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.232</v>
+        <v>0.1713</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3394</v>
+        <v>-0.1075</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0256</v>
+        <v>2.364</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5794</v>
+        <v>0.3533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.605</v>
+        <v>2.0106</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0818</v>
+        <v>-2.3002</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3474</v>
+        <v>-0.1821</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2656</v>
+        <v>-2.1181</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7935</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-4.1661</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5208</v>
+        <v>1.3391</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3117</v>
+        <v>1.06</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8326</v>
+        <v>0.279</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8171</v>
+        <v>2.8889</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.7384</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8171</v>
+        <v>1.1505</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. TEJERO CASASAYAS</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.803</v>
+        <v>1.1348</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3899</v>
+        <v>0.8134</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.5869</v>
+        <v>0.3214</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7213</v>
+        <v>2.514</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06560000000000001</v>
+        <v>3.3161</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6557</v>
+        <v>-0.8021</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4902</v>
+        <v>2.9421</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1853</v>
+        <v>3.09</v>
       </c>
       <c r="L4" t="n">
-        <v>4.3049</v>
+        <v>-0.1479</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.769</v>
+        <v>-0.4281</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1197</v>
+        <v>0.226</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.6493</v>
+        <v>-0.6542</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1822</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1741</v>
+        <v>-2.9758</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5933</v>
+        <v>-0.3954</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2641</v>
+        <v>0.2438</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3292</v>
+        <v>-0.6392</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6707</v>
+        <v>0.6032</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8097</v>
+        <v>0.6032</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>E. TEJERO CASASAYAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8663</v>
+        <v>0.9905</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6423</v>
+        <v>4.9421</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7759</v>
+        <v>-3.9516</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0391</v>
+        <v>1.7213</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7358</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3033</v>
+        <v>1.6557</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4538</v>
+        <v>5.4902</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6143999999999999</v>
+        <v>1.1853</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1606</v>
+        <v>4.3049</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5853</v>
+        <v>-3.769</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1214</v>
+        <v>-1.1197</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4639</v>
+        <v>-2.6493</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1984</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6313</v>
+        <v>0.7808</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6155</v>
+        <v>0.8163</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0158</v>
+        <v>-0.0356</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4724</v>
+        <v>0.6707</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4724</v>
+        <v>1.8097</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.139</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.3205</v>
       </c>
       <c r="E6" t="n">
-        <v>0.649</v>
+        <v>0.9281</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1811</v>
+        <v>-0.6076</v>
       </c>
       <c r="G6" t="n">
-        <v>2.514</v>
+        <v>-2.0391</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3161</v>
+        <v>-0.7358</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8021</v>
+        <v>-1.3033</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9421</v>
+        <v>-0.4538</v>
       </c>
       <c r="K6" t="n">
-        <v>3.09</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1479</v>
+        <v>0.1606</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4281</v>
+        <v>-1.5853</v>
       </c>
       <c r="N6" t="n">
-        <v>0.226</v>
+        <v>-0.1214</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6542</v>
+        <v>-1.4639</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5871</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7</v>
+        <v>1.0855</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0794</v>
+        <v>0.9013</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7795</v>
+        <v>0.1842</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6032</v>
+        <v>1.4724</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6032</v>
+        <v>1.4724</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7565</v>
+        <v>-1.6544</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7719</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="F7" t="n">
         <v>-0.9846</v>
@@ -1000,10 +1000,10 @@
         <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0623</v>
+        <v>0.1644</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2551</v>
+        <v>0.3572</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1928</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.887</v>
+        <v>-1.8783</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7524</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6394</v>
+        <v>-2.3869</v>
       </c>
       <c r="G8" t="n">
         <v>-1.652</v>
@@ -1078,13 +1078,13 @@
         <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4235</v>
+        <v>0.4322</v>
       </c>
       <c r="T8" t="n">
-        <v>0.873</v>
+        <v>0.6292</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4495</v>
+        <v>-0.197</v>
       </c>
       <c r="V8" t="n">
         <v>0.3334</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9054</v>
+        <v>-2.0742</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0871</v>
+        <v>0.722</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9925</v>
+        <v>-2.7961</v>
       </c>
       <c r="G9" t="n">
         <v>0.0185</v>
@@ -1156,13 +1156,13 @@
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3168</v>
+        <v>0.5144</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0452</v>
+        <v>0.5896</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2716</v>
+        <v>-0.0752</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8135</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.723</v>
+        <v>-5.2414</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6516</v>
+        <v>-2.5066</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0715</v>
+        <v>-2.7348</v>
       </c>
       <c r="G10" t="n">
         <v>-5.4991</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0055</v>
+        <v>0.4761</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6518</v>
+        <v>0.4932</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3538</v>
+        <v>-0.0171</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2103</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7317</v>
+        <v>-6.1553</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2951</v>
+        <v>-2.887</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4367</v>
+        <v>-3.2683</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7897</v>
@@ -1312,13 +1312,13 @@
         <v>0.3968</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.3656</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3741</v>
+        <v>0.034</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.3996</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4129</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.5308</v>
+        <v>-10.9074</v>
       </c>
       <c r="E12" t="n">
-        <v>2.509999999999999</v>
+        <v>3.133499999999998</v>
       </c>
       <c r="F12" t="n">
         <v>-14.0409</v>
@@ -1369,7 +1369,7 @@
         <v>2.1975</v>
       </c>
       <c r="L12" t="n">
-        <v>5.796599999999999</v>
+        <v>5.796600000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-18.4355</v>
@@ -1390,13 +1390,13 @@
         <v>8.927300000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>4.0245</v>
+        <v>4.6479</v>
       </c>
       <c r="T12" t="n">
-        <v>4.762</v>
+        <v>5.3854</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7377</v>
+        <v>-0.7376999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>2.821399999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.257</v>
+        <v>7.291</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5726</v>
+        <v>6.4706</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6844</v>
+        <v>0.8204</v>
       </c>
       <c r="G13" t="n">
         <v>8.457800000000001</v>
@@ -1468,13 +1468,13 @@
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1247</v>
+        <v>0.1587</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5272</v>
+        <v>0.4252</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4025</v>
+        <v>-0.2665</v>
       </c>
       <c r="V13" t="n">
         <v>-0.532</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6418</v>
+        <v>5.3876</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4072</v>
+        <v>3.2441</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2346</v>
+        <v>2.1435</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1038</v>
+        <v>3.124</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6761</v>
+        <v>-0.9077</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4276</v>
+        <v>4.0317</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1189</v>
+        <v>3.2817</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3975</v>
+        <v>-0.4584</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2786</v>
+        <v>3.7401</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0151</v>
+        <v>-0.1577</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.4493</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7062</v>
+        <v>0.2916</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7774</v>
+        <v>1.5871</v>
       </c>
       <c r="Q14" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.579</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.1927</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.2778</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.8692</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.8692</v>
+      </c>
+      <c r="X14" t="n">
         <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.7774</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.1575</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.2436</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.4011</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.6032</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.0713</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2789</v>
+        <v>4.3426</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6319</v>
+        <v>1.5093</v>
       </c>
       <c r="F15" t="n">
-        <v>1.647</v>
+        <v>2.8334</v>
       </c>
       <c r="G15" t="n">
-        <v>3.124</v>
+        <v>1.1038</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9077</v>
+        <v>0.6761</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0317</v>
+        <v>0.4276</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2817</v>
+        <v>1.1189</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4584</v>
+        <v>1.3975</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7401</v>
+        <v>-0.2786</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1577</v>
+        <v>-0.0151</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4493</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2916</v>
+        <v>0.7062</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5871</v>
+        <v>2.7774</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.579</v>
+        <v>2.7774</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3014</v>
+        <v>-0.1417</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5271</v>
+        <v>-0.1416</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7743</v>
+        <v>-0.0001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8692</v>
+        <v>0.6032</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8692</v>
+        <v>0.532</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9763</v>
+        <v>2.9882</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0326</v>
+        <v>2.8285</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0563</v>
+        <v>0.1597</v>
       </c>
       <c r="G16" t="n">
         <v>1.9</v>
@@ -1702,13 +1702,13 @@
         <v>2.3806</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0249</v>
+        <v>0.0368</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5839</v>
+        <v>0.3799</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.343</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3373</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.353</v>
+        <v>1.9406</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1744</v>
+        <v>1.7663</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1786</v>
+        <v>0.1744</v>
       </c>
       <c r="G17" t="n">
         <v>0.3323</v>
@@ -1780,13 +1780,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1559</v>
+        <v>-0.2565</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3175</v>
+        <v>-0.0906</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1616</v>
+        <v>-0.1658</v>
       </c>
       <c r="V17" t="n">
         <v>0.6745</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0427</v>
+        <v>1.8811</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9883</v>
+        <v>1.2741</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0543</v>
+        <v>0.607</v>
       </c>
       <c r="G18" t="n">
         <v>0.8183</v>
@@ -1858,13 +1858,13 @@
         <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>0.034</v>
+        <v>-0.1275</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7993</v>
+        <v>0.0851</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7652</v>
+        <v>-0.2126</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MESA RUIZ</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6576</v>
+        <v>-0.6284</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7484</v>
+        <v>1.8421</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.406</v>
+        <v>-2.4705</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2973</v>
+        <v>-0.3238</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6199</v>
+        <v>-0.9728</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9172</v>
+        <v>0.6491</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2929</v>
+        <v>1.6388</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6101</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6827</v>
+        <v>2.4951</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5902</v>
+        <v>-1.9625</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0098</v>
+        <v>-0.1165</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6</v>
+        <v>-1.846</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1672</v>
+        <v>-0.8998</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1814</v>
+        <v>-0.0112</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0142</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. LOPEZ SAURA</t>
+          <t>A. MESA RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9494</v>
+        <v>-0.6619</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3511</v>
+        <v>0.7484</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5984</v>
+        <v>-1.4103</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2401</v>
+        <v>-0.2973</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7712</v>
+        <v>0.6199</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5312</v>
+        <v>-0.9172</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0683</v>
+        <v>1.2929</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5794</v>
+        <v>0.6101</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6827</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3084</v>
+        <v>-1.5902</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1918</v>
+        <v>0.0098</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1165</v>
+        <v>-1.6</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9919</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q20" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.1814</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.9919</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.1797</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.2551</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-0.07539999999999999</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-1.881</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-0.6745</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>M. LOPEZ SAURA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6189</v>
+        <v>-1.0795</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1279</v>
+        <v>-0.4531</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7468</v>
+        <v>-0.6264</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3238</v>
+        <v>-0.2401</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9728</v>
+        <v>-0.7712</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6491</v>
+        <v>0.5312</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6388</v>
+        <v>0.0683</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.5794</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4951</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9625</v>
+        <v>-0.3084</v>
       </c>
       <c r="N21" t="n">
+        <v>-0.1918</v>
+      </c>
+      <c r="O21" t="n">
         <v>-0.1165</v>
       </c>
-      <c r="O21" t="n">
-        <v>-1.846</v>
-      </c>
       <c r="P21" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8903</v>
+        <v>0.0496</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7254</v>
+        <v>0.1531</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1649</v>
+        <v>-0.1035</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.881</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2065</v>
+        <v>-0.6745</v>
       </c>
       <c r="X21" t="n">
         <v>-1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.792899999999999</v>
+        <v>-7.8899</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.2913</v>
+        <v>-5.1893</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5015</v>
+        <v>-2.7006</v>
       </c>
       <c r="G22" t="n">
         <v>-4.4337</v>
@@ -2170,13 +2170,13 @@
         <v>1.7855</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6766</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4307</v>
+        <v>-0.3286</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2459</v>
+        <v>-0.445</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4842</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>11.5309</v>
+        <v>13.5714</v>
       </c>
       <c r="E23" t="n">
-        <v>14.0409</v>
+        <v>14.041</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5101</v>
+        <v>-0.4693999999999998</v>
       </c>
       <c r="G23" t="n">
         <v>10.4413</v>
@@ -2230,7 +2230,7 @@
         <v>14.5741</v>
       </c>
       <c r="M23" t="n">
-        <v>-7.9941</v>
+        <v>-7.994099999999999</v>
       </c>
       <c r="N23" t="n">
         <v>-2.1974</v>
@@ -2248,13 +2248,13 @@
         <v>16.8627</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.0244</v>
+        <v>-1.9838</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7375999999999998</v>
+        <v>0.7378</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.7619</v>
+        <v>-2.7214</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8216</v>
